--- a/data/trans_orig/Q17F_D_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q17F_D_R-Habitat-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo de espera medio en días hasta la consulta en el centro sanitario</t>
+          <t>Tiempo de espera medio en días hasta la consulta en el centro sanitario (tasa de respuesta: 94,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,13; 23,82</t>
+          <t>6,95; 24,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,99; 16,22</t>
+          <t>6,58; 15,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,25; 19,5</t>
+          <t>8,1; 19,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,93; 28,16</t>
+          <t>9,56; 25,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,12; 7,17</t>
+          <t>3,16; 7,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,52; 11,11</t>
+          <t>4,58; 11,61</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,96; 36,76</t>
+          <t>8,56; 33,96</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,91; 24,26</t>
+          <t>9,6; 23,05</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,39; 12,01</t>
+          <t>5,27; 12,22</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,34; 11,72</t>
+          <t>6,22; 11,82</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9,77; 23,95</t>
+          <t>9,79; 23,85</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10,56; 21,24</t>
+          <t>11,15; 20,75</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,24; 12,48</t>
+          <t>3,94; 11,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,46; 13,08</t>
+          <t>6,44; 12,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,43; 9,52</t>
+          <t>4,55; 9,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,2; 25,0</t>
+          <t>9,88; 25,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,96; 15,59</t>
+          <t>5,81; 15,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,46; 16,57</t>
+          <t>7,64; 16,52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,02; 16,8</t>
+          <t>6,79; 16,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,81; 32,05</t>
+          <t>17,08; 31,7</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,95; 12,51</t>
+          <t>6,07; 12,5</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,68; 13,63</t>
+          <t>7,87; 14,24</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,6; 12,15</t>
+          <t>6,36; 12,16</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,53; 24,62</t>
+          <t>15,26; 25,53</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,92; 15,6</t>
+          <t>8,12; 16,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,33; 18,22</t>
+          <t>7,97; 17,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,65; 24,15</t>
+          <t>10,18; 24,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,12; 49,78</t>
+          <t>17,48; 55,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,39; 21,68</t>
+          <t>9,43; 21,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,2; 18,79</t>
+          <t>7,16; 18,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,61; 22,36</t>
+          <t>11,88; 22,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,88; 35,55</t>
+          <t>18,43; 35,17</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,68; 16,65</t>
+          <t>9,74; 17,06</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8,61; 15,37</t>
+          <t>8,38; 15,93</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12,16; 20,63</t>
+          <t>11,96; 20,75</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>19,82; 37,56</t>
+          <t>20,3; 37,6</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,53; 26,28</t>
+          <t>7,41; 24,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,82; 13,57</t>
+          <t>5,62; 13,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,41; 12,47</t>
+          <t>5,38; 13,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23,41; 51,41</t>
+          <t>24,08; 52,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,56; 13,28</t>
+          <t>6,37; 12,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,34; 14,23</t>
+          <t>7,42; 14,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,12; 25,41</t>
+          <t>9,96; 25,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,69; 27,82</t>
+          <t>13,08; 27,97</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,82; 14,8</t>
+          <t>7,75; 14,95</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,44; 12,65</t>
+          <t>7,46; 12,9</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,91; 19,32</t>
+          <t>8,83; 19,76</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,66; 32,82</t>
+          <t>17,54; 32,35</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,2; 14,57</t>
+          <t>8,3; 14,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,15; 12,19</t>
+          <t>8,15; 12,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,15; 12,81</t>
+          <t>7,95; 12,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19,03; 31,65</t>
+          <t>19,08; 30,77</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,54; 11,44</t>
+          <t>7,36; 11,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,07; 12,18</t>
+          <t>8,03; 12,11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,15; 18,26</t>
+          <t>11,11; 17,63</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>16,83; 24,8</t>
+          <t>16,08; 24,38</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,27; 11,49</t>
+          <t>8,25; 11,52</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,66; 11,82</t>
+          <t>8,55; 11,49</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10,45; 14,83</t>
+          <t>10,3; 14,7</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,76; 26,01</t>
+          <t>18,85; 25,82</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q17F_D_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q17F_D_R-Habitat-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16,4</t>
+          <t>16,77</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>13,65</t>
+          <t>14,21</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>14,77</t>
+          <t>15,25</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,95; 24,65</t>
+          <t>7,14; 24,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,58; 15,71</t>
+          <t>6,68; 15,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,1; 19,78</t>
+          <t>8,36; 20,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,56; 25,82</t>
+          <t>9,88; 28,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,16; 7,03</t>
+          <t>3,2; 7,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,58; 11,61</t>
+          <t>4,57; 11,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,56; 33,96</t>
+          <t>8,69; 32,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,6; 23,05</t>
+          <t>9,95; 21,99</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,27; 12,22</t>
+          <t>5,19; 11,47</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,22; 11,82</t>
+          <t>6,06; 11,58</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9,79; 23,85</t>
+          <t>9,69; 23,36</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,15; 20,75</t>
+          <t>11,5; 21,01</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14,99</t>
+          <t>15,27</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>22,77</t>
+          <t>22,08</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>19,21</t>
+          <t>19,0</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,94; 11,03</t>
+          <t>4,24; 11,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,44; 12,92</t>
+          <t>6,36; 13,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,55; 9,64</t>
+          <t>4,41; 9,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,88; 25,28</t>
+          <t>10,38; 24,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,81; 15,57</t>
+          <t>6,0; 15,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,64; 16,52</t>
+          <t>7,42; 16,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,79; 16,68</t>
+          <t>7,48; 16,39</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,08; 31,7</t>
+          <t>16,56; 30,21</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,07; 12,5</t>
+          <t>6,07; 12,65</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,87; 14,24</t>
+          <t>7,82; 13,77</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,36; 12,16</t>
+          <t>6,35; 12,56</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,26; 25,53</t>
+          <t>15,25; 24,99</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26,43</t>
+          <t>25,59</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>25,1</t>
+          <t>25,43</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>25,72</t>
+          <t>25,5</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,12; 16,03</t>
+          <t>8,2; 16,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,97; 17,97</t>
+          <t>8,3; 17,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,18; 24,71</t>
+          <t>9,81; 24,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,48; 55,14</t>
+          <t>17,16; 49,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,43; 21,13</t>
+          <t>9,08; 19,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,16; 18,05</t>
+          <t>7,12; 17,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,88; 22,16</t>
+          <t>11,79; 22,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,43; 35,17</t>
+          <t>18,6; 34,49</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,74; 17,06</t>
+          <t>9,55; 17,23</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8,38; 15,93</t>
+          <t>8,79; 15,54</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11,96; 20,75</t>
+          <t>12,18; 20,54</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>20,3; 37,6</t>
+          <t>20,07; 35,68</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33,59</t>
+          <t>35,54</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>21,02</t>
+          <t>26,11</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>25,65</t>
+          <t>29,98</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,41; 24,03</t>
+          <t>7,48; 23,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,62; 13,92</t>
+          <t>5,54; 14,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,38; 13,39</t>
+          <t>5,35; 12,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24,08; 52,47</t>
+          <t>25,73; 53,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,37; 12,68</t>
+          <t>6,71; 13,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,42; 14,59</t>
+          <t>7,4; 14,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,96; 25,45</t>
+          <t>10,18; 26,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,08; 27,97</t>
+          <t>21,16; 33,95</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,75; 14,95</t>
+          <t>7,94; 14,9</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,46; 12,9</t>
+          <t>7,55; 12,6</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,83; 19,76</t>
+          <t>8,99; 19,3</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,54; 32,35</t>
+          <t>24,84; 37,88</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23,77</t>
+          <t>24,21</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>20,76</t>
+          <t>22,6</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>22,01</t>
+          <t>23,29</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,3; 14,3</t>
+          <t>8,24; 15,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,15; 12,21</t>
+          <t>8,18; 12,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,95; 12,46</t>
+          <t>7,91; 12,55</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19,08; 30,77</t>
+          <t>19,91; 31,39</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,36; 11,28</t>
+          <t>7,57; 11,53</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,03; 12,11</t>
+          <t>8,17; 12,7</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,11; 17,63</t>
+          <t>10,97; 17,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>16,08; 24,38</t>
+          <t>19,79; 26,52</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,25; 11,52</t>
+          <t>8,13; 11,58</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,55; 11,49</t>
+          <t>8,67; 11,61</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10,3; 14,7</t>
+          <t>10,25; 14,47</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,85; 25,82</t>
+          <t>20,54; 26,97</t>
         </is>
       </c>
     </row>
